--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区来广营西路甲9号</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
     </row>
@@ -12528,17 +12528,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -12592,17 +12592,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -12624,17 +12624,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -12848,17 +12848,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -12880,17 +12880,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -13040,17 +13040,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
@@ -13136,17 +13136,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13168,17 +13168,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13333,12 +13333,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13483,22 +13483,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13547,22 +13547,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
@@ -13584,17 +13584,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -13621,12 +13621,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,29 +13636,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区来广营西路甲9号</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
     </row>
@@ -12528,17 +12528,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12560,17 +12560,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -12688,17 +12688,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
@@ -12912,17 +12912,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -13040,17 +13040,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -13168,17 +13168,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13323,22 +13323,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13515,22 +13515,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
@@ -12624,17 +12624,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -12656,17 +12656,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -12720,17 +12720,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12789,12 +12789,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
@@ -12880,17 +12880,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -13072,17 +13072,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -13104,17 +13104,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
@@ -13163,22 +13163,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -13200,17 +13200,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13483,22 +13483,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13515,22 +13515,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13552,17 +13552,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
@@ -13643,22 +13643,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12597,12 +12597,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
@@ -12624,17 +12624,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -12656,17 +12656,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
@@ -12752,17 +12752,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -12816,17 +12816,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -12944,17 +12944,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
@@ -13099,22 +13099,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
@@ -13301,12 +13301,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13365,12 +13365,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13392,17 +13392,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13515,22 +13515,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13547,22 +13547,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13616,17 +13616,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区来广营西路甲9号</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -12688,17 +12688,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -12752,17 +12752,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -13040,17 +13040,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
@@ -13104,17 +13104,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -13136,17 +13136,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13323,22 +13323,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13424,17 +13424,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13488,17 +13488,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13515,22 +13515,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13547,22 +13547,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13584,17 +13584,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,29 +13604,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区来广营西路甲9号</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
     </row>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -12619,22 +12619,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
@@ -12656,17 +12656,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
@@ -12752,17 +12752,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
@@ -12880,17 +12880,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13323,22 +13323,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13365,12 +13365,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13424,17 +13424,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13456,17 +13456,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13483,22 +13483,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13515,22 +13515,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13557,12 +13557,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
@@ -13584,17 +13584,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13648,17 +13648,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12592,17 +12592,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -12651,22 +12651,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -12816,17 +12816,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -12880,17 +12880,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -12912,17 +12912,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12944,17 +12944,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13323,22 +13323,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13355,22 +13355,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13515,22 +13515,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13547,22 +13547,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,29 +13604,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -13648,17 +13648,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区来广营西路甲9号</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
     </row>
@@ -12528,17 +12528,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -12560,17 +12560,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -12693,12 +12693,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
@@ -12875,22 +12875,22 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
@@ -13136,17 +13136,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13264,17 +13264,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13323,22 +13323,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13355,22 +13355,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13515,22 +13515,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13547,22 +13547,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
@@ -13616,17 +13616,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
@@ -12619,22 +12619,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -12752,17 +12752,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -12848,17 +12848,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
@@ -13109,12 +13109,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
@@ -13264,17 +13264,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13323,22 +13323,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13355,22 +13355,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13547,22 +13547,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
@@ -12592,17 +12592,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -12816,17 +12816,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -12944,17 +12944,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -13099,22 +13099,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13333,12 +13333,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13483,22 +13483,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13547,22 +13547,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
@@ -13621,12 +13621,12 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13648,17 +13648,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区来广营西路甲9号</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -12565,12 +12565,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -12624,17 +12624,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12661,12 +12661,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -12784,17 +12784,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -12816,17 +12816,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -12848,17 +12848,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
@@ -13072,17 +13072,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
@@ -13104,17 +13104,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13296,17 +13296,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13323,22 +13323,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13355,22 +13355,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13483,22 +13483,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13515,22 +13515,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13547,22 +13547,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13616,17 +13616,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -13648,17 +13648,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区来广营西路甲9号</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -12683,22 +12683,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12720,17 +12720,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -12752,17 +12752,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -13104,17 +13104,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -13136,17 +13136,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -13168,17 +13168,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -13200,17 +13200,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13323,22 +13323,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13355,22 +13355,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13547,22 +13547,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -12656,17 +12656,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
@@ -12848,17 +12848,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -12880,17 +12880,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
@@ -13008,17 +13008,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -13072,17 +13072,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -13136,17 +13136,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -13200,17 +13200,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13333,12 +13333,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13355,22 +13355,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13424,17 +13424,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13483,22 +13483,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13557,12 +13557,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
@@ -13653,12 +13653,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
     </row>
@@ -12528,17 +12528,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12560,17 +12560,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -12592,17 +12592,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -12688,17 +12688,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
@@ -12816,17 +12816,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -13072,17 +13072,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -13104,17 +13104,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -13200,17 +13200,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -13269,12 +13269,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13323,22 +13323,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13483,22 +13483,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13515,22 +13515,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13579,22 +13579,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13643,22 +13643,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区来广营西路甲9号</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -12528,17 +12528,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
@@ -12656,17 +12656,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
@@ -12880,17 +12880,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13323,22 +13323,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13493,12 +13493,12 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13515,22 +13515,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13584,17 +13584,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -13616,17 +13616,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区来广营西路甲9号</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -12528,17 +12528,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
@@ -12592,17 +12592,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
@@ -12752,17 +12752,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -12784,17 +12784,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -12880,17 +12880,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -12912,17 +12912,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
@@ -13040,17 +13040,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -13136,17 +13136,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -13168,17 +13168,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13323,22 +13323,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13355,22 +13355,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13456,17 +13456,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13483,22 +13483,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13557,12 +13557,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13572,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
@@ -13616,17 +13616,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,29 +13636,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（38家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（48家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（36条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（38家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（48家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（36条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -12528,17 +12528,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
@@ -12693,12 +12693,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
@@ -12779,22 +12779,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
@@ -12976,17 +12976,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -13200,17 +13200,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13483,22 +13483,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13515,22 +13515,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13579,22 +13579,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -13616,17 +13616,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,29 +13636,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（38家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（48家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（36条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（38家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（48家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（36条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12580,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
@@ -12592,17 +12592,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12752,17 +12752,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12932,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -13040,17 +13040,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,7 +13060,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -13077,12 +13077,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13323,22 +13323,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13483,22 +13483,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13515,22 +13515,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13557,12 +13557,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
@@ -13611,22 +13611,22 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,29 +13636,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（38家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（48家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（36条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（38家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（48家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（36条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区来广营西路甲9号</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11610,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
     </row>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,29 +12548,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12656,17 +12656,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -12688,17 +12688,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12740,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
@@ -12752,17 +12752,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -12784,17 +12784,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
@@ -12939,22 +12939,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -13045,12 +13045,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -13168,17 +13168,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -13269,12 +13269,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13333,12 +13333,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13483,22 +13483,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13515,22 +13515,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13584,17 +13584,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,29 +13604,29 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,29 +13636,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（38家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（48家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（36条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（38家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（48家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（36条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10524,7 +10524,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区来广营西路甲9号</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12597,12 +12597,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12612,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
@@ -12693,12 +12693,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,29 +12772,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12804,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -12944,17 +12944,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13092,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,29 +13124,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,29 +13156,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13188,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13328,17 +13328,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13355,22 +13355,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13392,17 +13392,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13483,22 +13483,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13515,22 +13515,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13579,22 +13579,22 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
@@ -13643,22 +13643,22 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
     </row>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -12523,22 +12523,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
@@ -12560,17 +12560,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,29 +12580,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -12624,17 +12624,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,29 +12644,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,29 +12676,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12708,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,29 +12740,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
@@ -12784,17 +12784,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -12816,17 +12816,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12836,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12868,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12900,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -12944,17 +12944,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,29 +12964,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +12996,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13028,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13060,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
@@ -13131,7 +13131,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13168,17 +13168,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -13200,17 +13200,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13259,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13291,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13323,22 +13323,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13360,17 +13360,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13387,22 +13387,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13419,22 +13419,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13451,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13483,22 +13483,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13552,17 +13552,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -13616,17 +13616,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13636,7 +13636,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13653,12 +13653,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8818</v>
+        <v>8820</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8808</v>
+        <v>8810</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-10</v>
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E435"/>
+  <dimension ref="A1:E437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6528,14 +6528,14 @@
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C268" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D268" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E268" s="3" t="n">
         <v>0</v>
@@ -6549,14 +6549,14 @@
       </c>
       <c r="B269" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C269" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D269" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E269" s="3" t="n">
         <v>0</v>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C270" s="3" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B271" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C271" s="3" t="n">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C272" s="3" t="n">
@@ -6633,101 +6633,101 @@
       </c>
       <c r="B273" s="3" t="inlineStr">
         <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr">
+        <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C273" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D273" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E273" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="4" t="inlineStr">
+      <c r="C275" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D275" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E275" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B274" s="4" t="inlineStr">
+      <c r="B276" s="4" t="inlineStr">
         <is>
           <t>江苏</t>
         </is>
       </c>
-      <c r="C274" s="4" t="n">
+      <c r="C276" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="D274" s="4" t="n">
+      <c r="D276" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="E274" s="4" t="n">
+      <c r="E276" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="4" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B275" s="4" t="inlineStr">
+      <c r="B277" s="4" t="inlineStr">
         <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="C275" s="4" t="n">
+      <c r="C277" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="D275" s="4" t="n">
+      <c r="D277" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="E275" s="4" t="n">
+      <c r="E277" s="4" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="3" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B276" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C276" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="D276" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="E276" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="3" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B277" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C277" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D277" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E277" s="3" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -6738,14 +6738,14 @@
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C278" s="3" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="D278" s="3" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="E278" s="3" t="n">
         <v>0</v>
@@ -6759,14 +6759,14 @@
       </c>
       <c r="B279" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C279" s="3" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D279" s="3" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E279" s="3" t="n">
         <v>0</v>
@@ -6780,14 +6780,14 @@
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C280" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D280" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E280" s="3" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="B281" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C281" s="3" t="n">
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C282" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D282" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E282" s="3" t="n">
         <v>0</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="B283" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C283" s="3" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E283" s="3" t="n">
         <v>0</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C284" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E284" s="3" t="n">
         <v>0</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="B285" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C285" s="3" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D285" s="3" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="E285" s="3" t="n">
         <v>0</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C286" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D286" s="3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E286" s="3" t="n">
         <v>0</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="B287" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C287" s="3" t="n">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="D287" s="3" t="n">
-        <v>82</v>
+        <v>29</v>
       </c>
       <c r="E287" s="3" t="n">
         <v>0</v>
@@ -6948,14 +6948,14 @@
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C288" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D288" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E288" s="3" t="n">
         <v>0</v>
@@ -6969,14 +6969,14 @@
       </c>
       <c r="B289" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C289" s="3" t="n">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="D289" s="3" t="n">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="E289" s="3" t="n">
         <v>0</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C290" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D290" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E290" s="3" t="n">
         <v>0</v>
@@ -7011,14 +7011,14 @@
       </c>
       <c r="B291" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C291" s="3" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D291" s="3" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E291" s="3" t="n">
         <v>0</v>
@@ -7032,14 +7032,14 @@
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C292" s="3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D292" s="3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E292" s="3" t="n">
         <v>0</v>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="B293" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C293" s="3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D293" s="3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E293" s="3" t="n">
         <v>0</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C294" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D294" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E294" s="3" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="B295" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C295" s="3" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D295" s="3" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E295" s="3" t="n">
         <v>0</v>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C296" s="3" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D296" s="3" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E296" s="3" t="n">
         <v>0</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="B297" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C297" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D297" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E297" s="3" t="n">
         <v>0</v>
@@ -7158,14 +7158,14 @@
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C298" s="3" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D298" s="3" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E298" s="3" t="n">
         <v>0</v>
@@ -7179,14 +7179,14 @@
       </c>
       <c r="B299" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C299" s="3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D299" s="3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E299" s="3" t="n">
         <v>0</v>
@@ -7200,14 +7200,14 @@
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C300" s="3" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D300" s="3" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E300" s="3" t="n">
         <v>0</v>
@@ -7221,14 +7221,14 @@
       </c>
       <c r="B301" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C301" s="3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D301" s="3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E301" s="3" t="n">
         <v>0</v>
@@ -7242,80 +7242,80 @@
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C302" s="3" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D302" s="3" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E302" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="inlineStr">
+      <c r="A303" s="3" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B303" s="2" t="inlineStr">
-        <is>
-          <t>新疆</t>
-        </is>
-      </c>
-      <c r="C303" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D303" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E303" s="2" t="n">
-        <v>1</v>
+      <c r="B303" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C303" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D303" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E303" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C304" s="3" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D304" s="3" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="E304" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B305" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C305" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="D305" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E305" s="3" t="n">
-        <v>0</v>
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D305" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E305" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="306">
@@ -7326,14 +7326,14 @@
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C306" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D306" s="3" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E306" s="3" t="n">
         <v>0</v>
@@ -7347,14 +7347,14 @@
       </c>
       <c r="B307" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C307" s="3" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D307" s="3" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E307" s="3" t="n">
         <v>0</v>
@@ -7368,14 +7368,14 @@
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C308" s="3" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D308" s="3" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E308" s="3" t="n">
         <v>0</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="B309" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C309" s="3" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="D309" s="3" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="E309" s="3" t="n">
         <v>0</v>
@@ -7410,14 +7410,14 @@
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C310" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D310" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E310" s="3" t="n">
         <v>0</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="B311" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C311" s="3" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="D311" s="3" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="E311" s="3" t="n">
         <v>0</v>
@@ -7452,14 +7452,14 @@
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C312" s="3" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="D312" s="3" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="E312" s="3" t="n">
         <v>0</v>
@@ -7473,14 +7473,14 @@
       </c>
       <c r="B313" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C313" s="3" t="n">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="D313" s="3" t="n">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="E313" s="3" t="n">
         <v>0</v>
@@ -7494,14 +7494,14 @@
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C314" s="3" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D314" s="3" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E314" s="3" t="n">
         <v>0</v>
@@ -7515,14 +7515,14 @@
       </c>
       <c r="B315" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C315" s="3" t="n">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="D315" s="3" t="n">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="E315" s="3" t="n">
         <v>0</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C316" s="3" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D316" s="3" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E316" s="3" t="n">
         <v>0</v>
@@ -7557,14 +7557,14 @@
       </c>
       <c r="B317" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C317" s="3" t="n">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="D317" s="3" t="n">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="E317" s="3" t="n">
         <v>0</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C318" s="3" t="n">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="D318" s="3" t="n">
-        <v>109</v>
+        <v>16</v>
       </c>
       <c r="E318" s="3" t="n">
         <v>0</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="B319" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C319" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D319" s="3" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E319" s="3" t="n">
         <v>0</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C320" s="3" t="n">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="D320" s="3" t="n">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="E320" s="3" t="n">
         <v>0</v>
@@ -7641,14 +7641,14 @@
       </c>
       <c r="B321" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C321" s="3" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="D321" s="3" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="E321" s="3" t="n">
         <v>0</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C322" s="3" t="n">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="D322" s="3" t="n">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="E322" s="3" t="n">
         <v>0</v>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="B323" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C323" s="3" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="D323" s="3" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="E323" s="3" t="n">
         <v>0</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C324" s="3" t="n">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="D324" s="3" t="n">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="E324" s="3" t="n">
         <v>0</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="B325" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C325" s="3" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D325" s="3" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="E325" s="3" t="n">
         <v>0</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C326" s="3" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D326" s="3" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="E326" s="3" t="n">
         <v>0</v>
@@ -7767,7 +7767,7 @@
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C327" s="3" t="n">
@@ -7788,14 +7788,14 @@
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C328" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D328" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E328" s="3" t="n">
         <v>0</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="B329" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C329" s="3" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D329" s="3" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E329" s="3" t="n">
         <v>0</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C330" s="3" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="D330" s="3" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="E330" s="3" t="n">
         <v>0</v>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="B331" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C331" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D331" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E331" s="3" t="n">
         <v>0</v>
@@ -7872,14 +7872,14 @@
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C332" s="3" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D332" s="3" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E332" s="3" t="n">
         <v>0</v>
@@ -7893,14 +7893,14 @@
       </c>
       <c r="B333" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C333" s="3" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D333" s="3" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E333" s="3" t="n">
         <v>0</v>
@@ -7914,14 +7914,14 @@
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C334" s="3" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D334" s="3" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E334" s="3" t="n">
         <v>0</v>
@@ -7930,19 +7930,19 @@
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B335" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C335" s="3" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="D335" s="3" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E335" s="3" t="n">
         <v>0</v>
@@ -7951,19 +7951,19 @@
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C336" s="3" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D336" s="3" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E336" s="3" t="n">
         <v>0</v>
@@ -7977,14 +7977,14 @@
       </c>
       <c r="B337" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C337" s="3" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D337" s="3" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="E337" s="3" t="n">
         <v>0</v>
@@ -7998,14 +7998,14 @@
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C338" s="3" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D338" s="3" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E338" s="3" t="n">
         <v>0</v>
@@ -8019,14 +8019,14 @@
       </c>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C339" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D339" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E339" s="3" t="n">
         <v>0</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C340" s="3" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D340" s="3" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E340" s="3" t="n">
         <v>0</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="B341" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C341" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D341" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E341" s="3" t="n">
         <v>0</v>
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C342" s="3" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D342" s="3" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="E342" s="3" t="n">
         <v>0</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C343" s="3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D343" s="3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E343" s="3" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C344" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D344" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E344" s="3" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C345" s="3" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D345" s="3" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E345" s="3" t="n">
         <v>0</v>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C346" s="3" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="D346" s="3" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="E346" s="3" t="n">
         <v>0</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C347" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D347" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E347" s="3" t="n">
         <v>0</v>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C348" s="3" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="D348" s="3" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="E348" s="3" t="n">
         <v>0</v>
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C349" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D349" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E349" s="3" t="n">
         <v>0</v>
@@ -8250,14 +8250,14 @@
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C350" s="3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D350" s="3" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E350" s="3" t="n">
         <v>0</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C351" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D351" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E351" s="3" t="n">
         <v>0</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C352" s="3" t="n">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="D352" s="3" t="n">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="E352" s="3" t="n">
         <v>0</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C353" s="3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D353" s="3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E353" s="3" t="n">
         <v>0</v>
@@ -8334,14 +8334,14 @@
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C354" s="3" t="n">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="D354" s="3" t="n">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="E354" s="3" t="n">
         <v>0</v>
@@ -8355,14 +8355,14 @@
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C355" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D355" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E355" s="3" t="n">
         <v>0</v>
@@ -8376,14 +8376,14 @@
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C356" s="3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D356" s="3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E356" s="3" t="n">
         <v>0</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C357" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D357" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E357" s="3" t="n">
         <v>0</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C358" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D358" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E358" s="3" t="n">
         <v>0</v>
@@ -8439,14 +8439,14 @@
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C359" s="3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D359" s="3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E359" s="3" t="n">
         <v>0</v>
@@ -8460,14 +8460,14 @@
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C360" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D360" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E360" s="3" t="n">
         <v>0</v>
@@ -8481,14 +8481,14 @@
       </c>
       <c r="B361" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C361" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D361" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E361" s="3" t="n">
         <v>0</v>
@@ -8502,14 +8502,14 @@
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C362" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D362" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E362" s="3" t="n">
         <v>0</v>
@@ -8523,49 +8523,49 @@
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C363" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D363" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E363" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="inlineStr">
+      <c r="A364" s="3" t="inlineStr">
         <is>
           <t>蔚来</t>
         </is>
       </c>
-      <c r="B364" s="2" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C364" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="D364" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="E364" s="2" t="n">
-        <v>1</v>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C364" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D364" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E364" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B365" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C365" s="3" t="n">
@@ -8579,24 +8579,24 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="3" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B366" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C366" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D366" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E366" s="3" t="n">
-        <v>0</v>
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="D366" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="E366" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="367">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C367" s="3" t="n">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C368" s="3" t="n">
@@ -8649,14 +8649,14 @@
       </c>
       <c r="B369" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C369" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D369" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E369" s="3" t="n">
         <v>0</v>
@@ -8670,7 +8670,7 @@
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C370" s="3" t="n">
@@ -8691,14 +8691,14 @@
       </c>
       <c r="B371" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C371" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D371" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E371" s="3" t="n">
         <v>0</v>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C372" s="3" t="n">
@@ -8733,14 +8733,14 @@
       </c>
       <c r="B373" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C373" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D373" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E373" s="3" t="n">
         <v>0</v>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C374" s="3" t="n">
@@ -8770,19 +8770,19 @@
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B375" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C375" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D375" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E375" s="3" t="n">
         <v>0</v>
@@ -8791,19 +8791,19 @@
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C376" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D376" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E376" s="3" t="n">
         <v>0</v>
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C377" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D377" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E377" s="3" t="n">
         <v>0</v>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C378" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D378" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E378" s="3" t="n">
         <v>0</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C379" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D379" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E379" s="3" t="n">
         <v>0</v>
@@ -8880,14 +8880,14 @@
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C380" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D380" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E380" s="3" t="n">
         <v>0</v>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C381" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D381" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E381" s="3" t="n">
         <v>0</v>
@@ -8922,14 +8922,14 @@
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C382" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D382" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E382" s="3" t="n">
         <v>0</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C383" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D383" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E383" s="3" t="n">
         <v>0</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C384" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D384" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E384" s="3" t="n">
         <v>0</v>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="B385" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C385" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D385" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E385" s="3" t="n">
         <v>0</v>
@@ -9006,14 +9006,14 @@
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C386" s="3" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="D386" s="3" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="E386" s="3" t="n">
         <v>0</v>
@@ -9027,14 +9027,14 @@
       </c>
       <c r="B387" s="3" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C387" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D387" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E387" s="3" t="n">
         <v>0</v>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C388" s="3" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="D388" s="3" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="E388" s="3" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B389" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C389" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D389" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E389" s="3" t="n">
         <v>0</v>
@@ -9090,14 +9090,14 @@
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C390" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D390" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E390" s="3" t="n">
         <v>0</v>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="B391" s="3" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C391" s="3" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D391" s="3" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E391" s="3" t="n">
         <v>0</v>
@@ -9132,14 +9132,14 @@
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C392" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D392" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E392" s="3" t="n">
         <v>0</v>
@@ -9153,14 +9153,14 @@
       </c>
       <c r="B393" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C393" s="3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D393" s="3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E393" s="3" t="n">
         <v>0</v>
@@ -9174,14 +9174,14 @@
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C394" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D394" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E394" s="3" t="n">
         <v>0</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="B395" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C395" s="3" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D395" s="3" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E395" s="3" t="n">
         <v>0</v>
@@ -9216,14 +9216,14 @@
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C396" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D396" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E396" s="3" t="n">
         <v>0</v>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="B397" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C397" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D397" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E397" s="3" t="n">
         <v>0</v>
@@ -9258,14 +9258,14 @@
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C398" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D398" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E398" s="3" t="n">
         <v>0</v>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="B399" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C399" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D399" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E399" s="3" t="n">
         <v>0</v>
@@ -9300,14 +9300,14 @@
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C400" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D400" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E400" s="3" t="n">
         <v>0</v>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="B401" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C401" s="3" t="n">
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C402" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D402" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E402" s="3" t="n">
         <v>0</v>
@@ -9363,14 +9363,14 @@
       </c>
       <c r="B403" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C403" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D403" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E403" s="3" t="n">
         <v>0</v>
@@ -9384,59 +9384,59 @@
       </c>
       <c r="B404" s="3" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C404" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D404" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E404" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="3" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C405" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D405" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E405" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="3" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C404" s="3" t="n">
+      <c r="C406" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D404" s="3" t="n">
+      <c r="D406" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E404" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B405" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C405" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="D405" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="E405" s="4" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B406" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C406" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="D406" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="E406" s="4" t="n">
-        <v>-1</v>
+      <c r="E406" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="407">
@@ -9447,14 +9447,14 @@
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C407" s="4" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="D407" s="4" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="E407" s="4" t="n">
         <v>-1</v>
@@ -9468,59 +9468,59 @@
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C408" s="4" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D408" s="4" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E408" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="3" t="inlineStr">
+      <c r="A409" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B409" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C409" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="D409" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="E409" s="3" t="n">
-        <v>0</v>
+      <c r="B409" s="4" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C409" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="D409" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E409" s="4" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="3" t="inlineStr">
+      <c r="A410" s="4" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B410" s="3" t="inlineStr">
-        <is>
-          <t>天津</t>
-        </is>
-      </c>
-      <c r="C410" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D410" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="E410" s="3" t="n">
-        <v>0</v>
+      <c r="B410" s="4" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="C410" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="D410" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="E410" s="4" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="411">
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C411" s="3" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D411" s="3" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E411" s="3" t="n">
         <v>0</v>
@@ -9552,14 +9552,14 @@
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C412" s="3" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D412" s="3" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E412" s="3" t="n">
         <v>0</v>
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C413" s="3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E413" s="3" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C414" s="3" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D414" s="3" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="E414" s="3" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C415" s="3" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D415" s="3" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E415" s="3" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C416" s="3" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="D416" s="3" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E416" s="3" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C417" s="3" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="D417" s="3" t="n">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="E417" s="3" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C418" s="3" t="n">
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C419" s="3" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="E419" s="3" t="n">
         <v>0</v>
@@ -9720,59 +9720,59 @@
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C420" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D420" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E420" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B421" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C421" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D421" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E421" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B422" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C420" s="3" t="n">
+      <c r="C422" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="D420" s="3" t="n">
+      <c r="D422" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="E420" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B421" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C421" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="D421" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="E421" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B422" s="2" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="C422" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="D422" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E422" s="2" t="n">
-        <v>1</v>
+      <c r="E422" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="423">
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C423" s="2" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="D423" s="2" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="E423" s="2" t="n">
         <v>1</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C424" s="2" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="D424" s="2" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E424" s="2" t="n">
         <v>1</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C425" s="2" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="D425" s="2" t="n">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="E425" s="2" t="n">
         <v>1</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>156</v>
+        <v>35</v>
       </c>
       <c r="D426" s="2" t="n">
-        <v>157</v>
+        <v>36</v>
       </c>
       <c r="E426" s="2" t="n">
         <v>1</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C427" s="2" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="D427" s="2" t="n">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="E427" s="2" t="n">
         <v>1</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="D428" s="2" t="n">
-        <v>66</v>
+        <v>157</v>
       </c>
       <c r="E428" s="2" t="n">
         <v>1</v>
@@ -9909,17 +9909,17 @@
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C429" s="2" t="n">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D429" s="2" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="E429" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
@@ -9930,17 +9930,17 @@
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C430" s="2" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D430" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E430" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C431" s="2" t="n">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="D431" s="2" t="n">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="E431" s="2" t="n">
         <v>2</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C432" s="2" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D432" s="2" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E432" s="2" t="n">
         <v>2</v>
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C433" s="2" t="n">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="D433" s="2" t="n">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="E433" s="2" t="n">
         <v>2</v>
@@ -10014,17 +10014,17 @@
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C434" s="2" t="n">
-        <v>201</v>
+        <v>46</v>
       </c>
       <c r="D434" s="2" t="n">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="E434" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="435">
@@ -10035,16 +10035,58 @@
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="D435" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="E435" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="D436" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="E436" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
           <t>江苏</t>
         </is>
       </c>
-      <c r="C435" s="2" t="n">
+      <c r="C437" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="D435" s="2" t="n">
+      <c r="D437" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="E435" s="2" t="n">
+      <c r="E437" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11421,7 +11463,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11436,7 +11478,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11490,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11463,7 +11505,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11652,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11625,7 +11667,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11679,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -11652,7 +11694,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11895,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11868,7 +11910,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11922,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -11895,7 +11937,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
     </row>
@@ -12528,17 +12570,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12548,7 +12590,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
@@ -12560,17 +12602,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12580,7 +12622,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -12592,17 +12634,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12612,29 +12654,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12644,7 +12686,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -12656,17 +12698,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12676,7 +12718,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12693,12 +12735,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12708,29 +12750,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12740,7 +12782,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12779,22 +12821,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12804,29 +12846,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12836,29 +12878,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12868,29 +12910,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12900,29 +12942,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12932,29 +12974,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12964,7 +13006,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
@@ -12976,17 +13018,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12996,29 +13038,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13028,29 +13070,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13060,29 +13102,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13092,29 +13134,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13124,7 +13166,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -13136,17 +13178,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13156,7 +13198,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -13168,17 +13210,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13188,29 +13230,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13220,7 +13262,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -13259,22 +13301,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13291,22 +13333,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13323,22 +13365,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13355,22 +13397,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13387,22 +13429,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13419,22 +13461,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13451,22 +13493,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13488,17 +13530,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13515,22 +13557,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13547,22 +13589,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13572,29 +13614,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13604,7 +13646,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
@@ -13648,17 +13690,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13668,7 +13710,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（38家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（48家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（36条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（38家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（48家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（36条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区来广营西路甲9号</t>
         </is>
       </c>
     </row>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -12565,22 +12565,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12590,29 +12590,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12622,29 +12622,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -12666,17 +12666,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12686,29 +12686,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -12735,12 +12735,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12750,29 +12750,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12782,29 +12782,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -12826,17 +12826,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12846,29 +12846,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
@@ -12895,12 +12895,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
@@ -12954,17 +12954,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12974,29 +12974,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13006,7 +13006,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -13045,22 +13045,22 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -13082,17 +13082,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13102,29 +13102,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13134,29 +13134,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -13178,17 +13178,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13198,29 +13198,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13230,29 +13230,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
@@ -13301,22 +13301,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13333,22 +13333,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13375,12 +13375,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13397,22 +13397,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13429,22 +13429,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13466,17 +13466,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13493,22 +13493,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13530,17 +13530,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13557,22 +13557,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13589,22 +13589,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13614,29 +13614,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
@@ -13658,17 +13658,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13678,7 +13678,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -13690,17 +13690,17 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -10551,7 +10551,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>北京市朝阳区王四营339号</t>
         </is>
       </c>
     </row>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区来广营西路甲9号</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
     </row>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
     </row>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
     </row>
@@ -12111,7 +12111,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
     </row>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
     </row>
@@ -12565,22 +12565,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12590,7 +12590,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -12629,22 +12629,22 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12654,29 +12654,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12686,29 +12686,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -12757,22 +12757,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -12794,17 +12794,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12814,29 +12814,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12846,29 +12846,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12878,29 +12878,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12910,29 +12910,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12942,29 +12942,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12974,29 +12974,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13006,7 +13006,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -13018,17 +13018,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13038,29 +13038,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
@@ -13082,17 +13082,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13102,29 +13102,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13134,29 +13134,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13166,29 +13166,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13198,29 +13198,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13230,29 +13230,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -13301,22 +13301,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13333,22 +13333,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13375,12 +13375,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13429,22 +13429,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13461,22 +13461,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13557,22 +13557,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（38家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（48家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（36条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（38家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（47家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（36条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,14 +665,14 @@
         <v>889</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.5%</t>
         </is>
       </c>
     </row>
@@ -875,10 +875,10 @@
         <v>8820</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8810</v>
+        <v>8811</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
@@ -4533,14 +4533,14 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="E173" s="4" t="n">
         <v>-1</v>
@@ -4554,14 +4554,14 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="E174" s="4" t="n">
         <v>-1</v>
@@ -4575,14 +4575,14 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>111</v>
+        <v>30</v>
       </c>
       <c r="E175" s="4" t="n">
         <v>-1</v>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C176" s="4" t="n">
@@ -4617,38 +4617,38 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="E177" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="4" t="inlineStr">
+      <c r="A178" s="3" t="inlineStr">
         <is>
           <t>小米</t>
         </is>
       </c>
-      <c r="B178" s="4" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D178" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="E178" s="4" t="n">
-        <v>-1</v>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -4659,14 +4659,14 @@
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E179" s="3" t="n">
         <v>0</v>
@@ -4680,14 +4680,14 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C180" s="3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E180" s="3" t="n">
         <v>0</v>
@@ -4701,14 +4701,14 @@
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E181" s="3" t="n">
         <v>0</v>
@@ -4722,14 +4722,14 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C182" s="3" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="E182" s="3" t="n">
         <v>0</v>
@@ -4743,14 +4743,14 @@
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C183" s="3" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="E183" s="3" t="n">
         <v>0</v>
@@ -4764,14 +4764,14 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C184" s="3" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="E184" s="3" t="n">
         <v>0</v>
@@ -10101,7 +10101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10109,6 +10109,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10137,6 +10138,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -10164,6 +10170,11 @@
           <t>贵州省贵阳市观山湖区金阳街道林城西路248号</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -10191,6 +10202,11 @@
           <t>河北省石家庄市长安区北二环与谈固大街交口西北角西行260米</t>
         </is>
       </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -10218,6 +10234,11 @@
           <t>湖南省永州市零陵区永州大道西侧潇湘汽车城西区第一排</t>
         </is>
       </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -10245,6 +10266,11 @@
           <t>广东省广州市南沙区中国铁建南沙环宇城3 号门中庭</t>
         </is>
       </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -10272,6 +10298,11 @@
           <t>江苏省盐城市东台市东台吾悦广场一楼中庭</t>
         </is>
       </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -10299,6 +10330,11 @@
           <t>江苏省苏州市张家港吾悦商场一楼1号门</t>
         </is>
       </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -10326,6 +10362,11 @@
           <t>湖北省武汉市江夏区佛祖岭街道高新六路与流芳一路交汇处伟星星悦广场（2号门）1楼</t>
         </is>
       </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -10353,6 +10394,11 @@
           <t>福建省泉州市石狮市八七路688号石狮德辉广场中庭</t>
         </is>
       </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -10380,6 +10426,11 @@
           <t>广州市海珠区琶洲蟠龙新街2号保利广场1层DY003A</t>
         </is>
       </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -10407,6 +10458,11 @@
           <t>河北省衡水市桃城区昌明大街与胜利西路转盘南行20米路西</t>
         </is>
       </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -10434,6 +10490,11 @@
           <t>江苏省无锡市江阴市宝城路77号</t>
         </is>
       </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -10461,6 +10522,11 @@
           <t>新疆维吾尔自治区阿克苏地区阿克苏市北京东路71号1F-100</t>
         </is>
       </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -10488,6 +10554,11 @@
           <t>江苏省苏州市吴江区开平路2299号L1-150铺位</t>
         </is>
       </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -10515,6 +10586,11 @@
           <t>浙江省湖州市吴兴区南街697号浙北大厦购物中心A侧门1号铺位</t>
         </is>
       </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -10542,6 +10618,11 @@
           <t>上海市浦东新区罗山路1589号</t>
         </is>
       </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -10551,7 +10632,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -10566,7 +10647,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>北京市朝阳区来广营西路甲9号</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10578,7 +10664,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>鸿蒙智行授权用户中心•北京王四营</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -10593,7 +10679,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>北京市朝阳区王四营339号</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10623,6 +10714,11 @@
           <t>吉林省通化市新胜北路2459号</t>
         </is>
       </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -10650,6 +10746,11 @@
           <t>四川省成都市郫都区望丛中路1199号成都蜀新天街 A 馆1F-29号30号</t>
         </is>
       </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -10677,6 +10778,11 @@
           <t>安徽省合肥市高新区望江西路888号银泰百 F11023-1024号华为授权服务中心</t>
         </is>
       </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -10704,6 +10810,11 @@
           <t>安徽省马鞍山市花山区湖西南路8号金鹰国际购物中心A01层F1018B商铺</t>
         </is>
       </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -10731,6 +10842,11 @@
           <t>山东省济南市历城区唐冶中路5199号银座·新辰天地L1层005号铺</t>
         </is>
       </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -10758,6 +10874,11 @@
           <t>山东省济宁市高新区海川路77号万象汇L152号商铺</t>
         </is>
       </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -10785,6 +10906,11 @@
           <t>广东省东莞市常平环常南路10号102室</t>
         </is>
       </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -10812,6 +10938,11 @@
           <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米</t>
         </is>
       </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -10839,6 +10970,11 @@
           <t>广东省汕头市龙湖区武夷山路1号瑞讯海湾汽车生活广场1号楼智界门店</t>
         </is>
       </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -10866,6 +11002,11 @@
           <t>广西壮族自治区柳州市城中区中山中路9号柳州风情港2栋1-1号</t>
         </is>
       </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -10893,6 +11034,11 @@
           <t>江苏省南通市崇川区环城南路88号华为授权体验店</t>
         </is>
       </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -10920,6 +11066,11 @@
           <t>江苏省无锡市宜兴市西氿大道92号</t>
         </is>
       </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -10947,6 +11098,11 @@
           <t>江苏省镇江市润州区官塘桥路299号</t>
         </is>
       </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -10974,6 +11130,11 @@
           <t>江西省南昌市青山湖区艾溪湖北路77号新城吾悦广场一层10003-1</t>
         </is>
       </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -11001,6 +11162,11 @@
           <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008</t>
         </is>
       </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -11028,6 +11194,11 @@
           <t>河北省衡水市昌明大街与胜利西路交叉口西南角</t>
         </is>
       </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -11055,6 +11226,11 @@
           <t>浙江省台州市椒江区中心大道555号青悦城111-2-112号商铺华为授权体验店</t>
         </is>
       </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -11082,6 +11258,11 @@
           <t>海南省三亚市吉阳区迎宾路393号</t>
         </is>
       </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -11109,6 +11290,11 @@
           <t>福州市仓山区潘墩路188号世纪金源购物中心3号门华为体验店</t>
         </is>
       </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -11136,6 +11322,11 @@
           <t>陕西省咸阳市秦都区玉泉东路10号咸阳丽彩万达广场1028号商铺（1F-C，2F-C）</t>
         </is>
       </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -11161,6 +11352,11 @@
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>陕西省安康市高新区钻石中路2号（鸿蒙智行）</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11183,6 +11379,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11211,6 +11408,11 @@
           <t>地址</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>历史状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -11238,6 +11440,11 @@
           <t>山东省济南市莱芜区汇源大街68号</t>
         </is>
       </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -11265,6 +11472,11 @@
           <t>广州市白云区机场路888号</t>
         </is>
       </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -11292,6 +11504,11 @@
           <t>南通市北大街111号华润万象润街16幢1606室</t>
         </is>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -11319,6 +11536,11 @@
           <t>江苏省徐州市经济技术开发区徐海路26号</t>
         </is>
       </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -11346,6 +11568,11 @@
           <t>甘肃省兰州市安宁区北滨河西路1746号</t>
         </is>
       </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -11373,6 +11600,11 @@
           <t>河南省濮阳市濮阳县胜利路与106国道交叉口向东500米路北</t>
         </is>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -11400,6 +11632,11 @@
           <t>河南省焦作市迎宾大道马村段西侧 (焦作康利达食品股份有限公司冷链物流园内)</t>
         </is>
       </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -11427,6 +11664,11 @@
           <t>商业银行大厦一层东侧店铺 湖滨北路101号 361012</t>
         </is>
       </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -11454,6 +11696,11 @@
           <t>霞美东路168号 霞美镇霞</t>
         </is>
       </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -11481,6 +11728,11 @@
           <t>城乡购物中心一层中庭</t>
         </is>
       </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -11508,6 +11760,11 @@
           <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -11535,6 +11792,11 @@
           <t>滨海万达一层</t>
         </is>
       </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -11544,22 +11806,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>小米汽车安徽合肥居巢区巢湖万达</t>
+          <t>小米汽车山西太原万柏林区太原新城吾悦</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>合肥市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>东塘路 80 号 合肥巢湖万达广场 1F</t>
+          <t>漪汾街和千峰北路交叉口太原新城吾悦广场3号门入口1F星巴克前</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11571,22 +11838,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>小米汽车山西太原万柏林区太原新城吾悦</t>
+          <t>小米汽车广东广州花都区花都雅乐城</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>广州市</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>漪汾街和千峰北路交叉口太原新城吾悦广场3号门入口1F星巴克前</t>
+          <t>永发路 14 号雅乐城一楼中庭</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11598,7 +11870,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>小米汽车广东广州花都区花都雅乐城</t>
+          <t>小米汽车广东梅州梅县区梅州天虹购物中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -11608,12 +11880,17 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>广州市</t>
+          <t>梅州市</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>永发路 14 号雅乐城一楼中庭</t>
+          <t>剑英大道南红星美凯龙首层梅州天虹购物中心中庭小米之家门口</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11625,22 +11902,27 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小米汽车广东梅州梅县区梅州天虹购物中心</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>梅州市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>剑英大道南红星美凯龙首层梅州天虹购物中心中庭小米之家门口</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11670,6 +11952,11 @@
           <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -11679,22 +11966,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车河南新乡长垣联华城广场</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>新乡市</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>博爱路与杏坛路交叉口联华城市广场一楼小米汽车展台</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11998,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南新乡长垣联华城广场</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -11716,12 +12008,17 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>新乡市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>博爱路与杏坛路交叉口联华城市广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11733,7 +12030,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11748,7 +12045,12 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11760,22 +12062,27 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车浙江台州仙居县仙居吾悦广场</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>台州市</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>泰和中路1号吾悦广场一楼1号门504点位</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11787,7 +12094,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>小米汽车浙江台州仙居县仙居吾悦广场</t>
+          <t>小米汽车浙江杭州萧山区加州阳光.开元广场</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -11797,12 +12104,17 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>台州市</t>
+          <t>杭州市</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>泰和中路1号吾悦广场一楼1号门504点位</t>
+          <t>金城路 333号</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11814,7 +12126,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>小米汽车浙江杭州萧山区加州阳光.开元广场</t>
+          <t>小米汽车浙江绍兴越城区龙湖镜湖天街</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -11824,12 +12136,17 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>杭州市</t>
+          <t>绍兴市</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>金城路 333号</t>
+          <t>越西路919号</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11841,22 +12158,27 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴越城区龙湖镜湖天街</t>
+          <t>小米汽车湖南长沙望城区砂之船奥特莱斯</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>绍兴市</t>
+          <t>长沙市</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>越西路919号</t>
+          <t>湖南省长沙市望城区金星北路378号LG层14-1</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11868,22 +12190,27 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>小米汽车湖南长沙望城区砂之船奥特莱斯</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>长沙市</t>
+          <t>漳州市</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>湖南省长沙市望城区金星北路378号LG层14-1</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11895,7 +12222,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11910,7 +12237,12 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -11922,76 +12254,91 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车贵州贵阳花溪区小河万科大都会</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>漳州市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>珠江路 374 号 万科大都会购物中心</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>小米汽车贵州贵阳花溪区小河万科大都会</t>
+          <t>小鹏汽车北京亦庄交付中心</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>贵阳市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>珠江路 374 号 万科大都会购物中心</t>
+          <t>北京市经济技术开发区科创三街15号A1幢</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 1 期</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄交付中心</t>
+          <t>上海崇明M515文创产业园新能源空间</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>北京市经济技术开发区科创三街15号A1幢</t>
+          <t>上海市崇明区宏海公路515号</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12003,22 +12350,27 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>上海崇明M515文创产业园新能源空间</t>
+          <t>昆明金科爱琴海购物公园新能源空间</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>昆明市</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>上海市崇明区宏海公路515号</t>
+          <t>昆明市西山区广福路488号</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12030,22 +12382,27 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>昆明金科爱琴海购物公园新能源空间</t>
+          <t>北京远洋乐提港新能源空间</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>昆明市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>昆明市西山区广福路488号</t>
+          <t>北京市通州区新华北路与通州北关桥交叉口东北角</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12057,22 +12414,27 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>北京远洋乐提港新能源空间</t>
+          <t>西夏万达广场新能源空间</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>银川市</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>北京市通州区新华北路与通州北关桥交叉口东北角</t>
+          <t>银川市西夏区金波北街75号</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12084,22 +12446,27 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>西夏万达广场新能源空间</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>银川市</t>
+          <t>佛山市</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>银川市西夏区金波北街75号</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12129,6 +12496,11 @@
           <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -12138,7 +12510,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>广州祈福缤纷世界新能源空间</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -12148,12 +12520,17 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>佛山市</t>
+          <t>广州市</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>广州市番禺区市广路8号钟村祈福新村祈福缤纷世界</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12165,22 +12542,27 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>广州祈福缤纷世界新能源空间</t>
+          <t>南宁江南蓝鲸世界新能源空间</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>广州市</t>
+          <t>南宁市</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>广州市番禺区市广路8号钟村祈福新村祈福缤纷世界</t>
+          <t>南宁市那洪街道江南经开区金凯路8号</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12574,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>南宁江南蓝鲸世界新能源空间</t>
+          <t>桂林客世界广场新能源空间</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -12202,12 +12584,17 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>南宁市</t>
+          <t>桂林市</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>南宁市那洪街道江南经开区金凯路8号</t>
+          <t>广西壮族自治区桂林市七星区漓江路19号</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12219,22 +12606,27 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>桂林客世界广场新能源空间</t>
+          <t>张家口光大新天地购物中心新能源空间</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>桂林市</t>
+          <t>张家口市</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>广西壮族自治区桂林市七星区漓江路19号</t>
+          <t>河北省张家口市宣化区宣府大街178号</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12246,22 +12638,27 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>张家口光大新天地购物中心新能源空间</t>
+          <t>兰州万达茂新能源空间</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>张家口市</t>
+          <t>兰州市</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>河北省张家口市宣化区宣府大街178号</t>
+          <t>兰州市七里河区南滨河西路1399号</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12273,49 +12670,59 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>兰州万达茂新能源空间</t>
+          <t>榆林国贸中心新能源空间</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>兰州市</t>
+          <t>榆林市</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>兰州市七里河区南滨河西路1399号</t>
+          <t>榆林市榆阳区人民中路115号</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>榆林国贸中心新能源空间</t>
+          <t>苏州大悦城城市展厅L1-52</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>榆林市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>榆林市榆阳区人民中路115号</t>
+          <t>江苏省苏州市相城区御窑路1999号L1-52</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12327,34 +12734,39 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>苏州大悦城城市展厅L1-52</t>
+          <t>台州黄岩特斯拉中心</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>台州市</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>江苏省苏州市相城区御窑路1999号L1-52</t>
+          <t>浙江省台州市黄岩区北城街道二环北路北侧地块手拉手汽车广场1幢</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>台州黄岩特斯拉中心</t>
+          <t>蔚来空间 | 绍兴新昌世贸</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -12364,39 +12776,49 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>台州市</t>
+          <t>绍兴市</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>浙江省台州市黄岩区北城街道二环北路北侧地块手拉手汽车广场1幢</t>
+          <t>浙江省新昌县南明街道鼓山东路196号新昌世贸广场一层编号为【005 】</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>蔚来空间 | 绍兴新昌世贸</t>
+          <t>华为智能生活馆•赤峰松山万达</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>绍兴市</t>
+          <t>赤峰市</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>浙江省新昌县南明街道鼓山东路196号新昌世贸广场一层编号为【005 】</t>
+          <t>内蒙古自治区赤峰市松山区友谊大街与迎金路交汇处</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12408,22 +12830,27 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•赤峰松山万达</t>
+          <t>鸿蒙智行授权用户中心•郑州中福汽车城</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>赤峰市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>内蒙古自治区赤峰市松山区友谊大街与迎金路交汇处</t>
+          <t>河南省郑州市经北六路与中州大道交叉口东800米路南中福汽车城7号</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12435,22 +12862,27 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•郑州中福汽车城</t>
+          <t>鸿蒙智行授权用户中心•宜昌发展大道</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>宜昌市</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>河南省郑州市经北六路与中州大道交叉口东800米路南中福汽车城7号</t>
+          <t>湖北省宜昌市西陵区发展大道44号</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12462,49 +12894,27 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•宜昌发展大道</t>
+          <t>鸿蒙智行授权用户中心•衡阳杨柳汽车城</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>宜昌市</t>
+          <t>衡阳市</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>湖北省宜昌市西陵区发展大道44号</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•衡阳杨柳汽车城</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>衡阳市</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
           <t>湖南省衡阳市蒸湘区杨柳汽贸城一期101号</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>连续在档 2 期</t>
         </is>
       </c>
     </row>
@@ -12565,22 +12975,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12590,29 +13000,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12622,7 +13032,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -12634,17 +13044,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12654,29 +13064,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12686,7 +13096,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -12698,17 +13108,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12718,29 +13128,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12750,7 +13160,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -12762,17 +13172,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12782,29 +13192,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12814,7 +13224,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
@@ -12826,17 +13236,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12846,29 +13256,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12878,29 +13288,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12910,7 +13320,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -12922,17 +13332,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12942,29 +13352,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12974,29 +13384,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13006,29 +13416,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13038,29 +13448,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13070,29 +13480,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13102,29 +13512,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13134,29 +13544,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13166,29 +13576,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13198,7 +13608,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13237,22 +13647,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13262,7 +13672,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
@@ -13301,22 +13711,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13375,12 +13785,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13402,17 +13812,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13429,22 +13839,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13461,22 +13871,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13493,22 +13903,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13525,22 +13935,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13557,22 +13967,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13589,22 +13999,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -13614,29 +14024,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -13646,7 +14056,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -13658,17 +14068,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13678,7 +14088,7 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
@@ -13695,12 +14105,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13710,7 +14120,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11379,7 +11379,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 2 期；本期存在高相似店名「揭阳宝泰行汽车销售服务有限公司」（疑似改名/合并，非真实关店）</t>
         </is>
       </c>
     </row>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 2 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 2 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>连续在档 2 期</t>
+          <t>连续在档 2 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -12975,22 +12975,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13192,29 +13192,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13224,29 +13224,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>AITO授权用户中心•阳泉开发区大连街</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13256,29 +13256,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13288,29 +13288,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13320,7 +13320,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
@@ -13332,17 +13332,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -13369,12 +13369,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>AITO授权用户中心•朔州振华汽车城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
         </is>
       </c>
     </row>
@@ -13423,22 +13423,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13448,29 +13448,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13480,29 +13480,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13512,29 +13512,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13544,29 +13544,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13576,29 +13576,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -13620,17 +13620,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
         </is>
       </c>
     </row>
@@ -13657,12 +13657,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>鸿蒙智行授权用户中心•南京江北新区</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
         </is>
       </c>
     </row>
@@ -13716,17 +13716,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13812,17 +13812,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13839,22 +13839,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>MAEXTRO尊界体验中心•北京三里屯</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13876,17 +13876,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13903,22 +13903,22 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13935,22 +13935,22 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -13967,22 +13967,22 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -13999,22 +13999,22 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -14036,17 +14036,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
@@ -14068,17 +14068,17 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -14088,29 +14088,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -9,9 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（38家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（47家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（36条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（30家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（44家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（29条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -851,17 +851,17 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1733</v>
+        <v>1479</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1753</v>
+        <v>1494</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1.0%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8820</v>
+        <v>8566</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8811</v>
+        <v>8552</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.2%</t>
         </is>
       </c>
     </row>
@@ -9451,76 +9451,76 @@
         </is>
       </c>
       <c r="C407" s="4" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D407" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E407" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="4" t="inlineStr">
+      <c r="A408" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B408" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C408" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="D408" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="E408" s="4" t="n">
-        <v>-1</v>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C408" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="D408" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="E408" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="4" t="inlineStr">
+      <c r="A409" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B409" s="4" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C409" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="D409" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="E409" s="4" t="n">
-        <v>-1</v>
+      <c r="B409" s="3" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C409" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D409" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E409" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="4" t="inlineStr">
+      <c r="A410" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B410" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C410" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="D410" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="E410" s="4" t="n">
-        <v>-1</v>
+      <c r="B410" s="3" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C410" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="D410" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="E410" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="411">
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C411" s="3" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D411" s="3" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E411" s="3" t="n">
         <v>0</v>
@@ -9556,10 +9556,10 @@
         </is>
       </c>
       <c r="C412" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D412" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E412" s="3" t="n">
         <v>0</v>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="C413" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D413" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E413" s="3" t="n">
         <v>0</v>
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="C414" s="3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D414" s="3" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E414" s="3" t="n">
         <v>0</v>
@@ -9619,10 +9619,10 @@
         </is>
       </c>
       <c r="C415" s="3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D415" s="3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E415" s="3" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C416" s="3" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D416" s="3" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="E416" s="3" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C417" s="3" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="D417" s="3" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="E417" s="3" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C418" s="3" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="D418" s="3" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="E418" s="3" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C419" s="3" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D419" s="3" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E419" s="3" t="n">
         <v>0</v>
@@ -9720,14 +9720,14 @@
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C420" s="3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D420" s="3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E420" s="3" t="n">
         <v>0</v>
@@ -9741,14 +9741,14 @@
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C421" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D421" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E421" s="3" t="n">
         <v>0</v>
@@ -9762,122 +9762,122 @@
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
+          <t>西藏</t>
+        </is>
+      </c>
+      <c r="C422" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D422" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E422" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B423" s="3" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="C423" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D423" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="E423" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B424" s="3" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C424" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D424" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="E424" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B425" s="3" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C425" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D425" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E425" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B426" s="3" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C426" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D426" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E426" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="3" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B427" s="3" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C422" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="D422" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="E422" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B423" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C423" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="D423" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="E423" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B424" s="2" t="inlineStr">
-        <is>
-          <t>吉林</t>
-        </is>
-      </c>
-      <c r="C424" s="2" t="n">
+      <c r="C427" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="D424" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E424" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B425" s="2" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C425" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="D425" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="E425" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B426" s="2" t="inlineStr">
-        <is>
-          <t>广西</t>
-        </is>
-      </c>
-      <c r="C426" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="D426" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="E426" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B427" s="2" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="C427" s="2" t="n">
-        <v>58</v>
-      </c>
-      <c r="D427" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="E427" s="2" t="n">
-        <v>1</v>
+      <c r="D427" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E427" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="428">
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="D428" s="2" t="n">
-        <v>157</v>
+        <v>79</v>
       </c>
       <c r="E428" s="2" t="n">
         <v>1</v>
@@ -9909,14 +9909,14 @@
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C429" s="2" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="D429" s="2" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="E429" s="2" t="n">
         <v>1</v>
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C430" s="2" t="n">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="D430" s="2" t="n">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="E430" s="2" t="n">
         <v>1</v>
@@ -9951,17 +9951,17 @@
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C431" s="2" t="n">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="D431" s="2" t="n">
-        <v>55</v>
+        <v>147</v>
       </c>
       <c r="E431" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -9972,17 +9972,17 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C432" s="2" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D432" s="2" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E432" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
@@ -9993,14 +9993,14 @@
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C433" s="2" t="n">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="D433" s="2" t="n">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="E433" s="2" t="n">
         <v>2</v>
@@ -10014,14 +10014,14 @@
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C434" s="2" t="n">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="D434" s="2" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="E434" s="2" t="n">
         <v>2</v>
@@ -10035,14 +10035,14 @@
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C435" s="2" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D435" s="2" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E435" s="2" t="n">
         <v>2</v>
@@ -10056,17 +10056,17 @@
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C436" s="2" t="n">
-        <v>201</v>
+        <v>41</v>
       </c>
       <c r="D436" s="2" t="n">
-        <v>204</v>
+        <v>43</v>
       </c>
       <c r="E436" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="437">
@@ -10077,14 +10077,14 @@
       </c>
       <c r="B437" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C437" s="2" t="n">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="D437" s="2" t="n">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="E437" s="2" t="n">
         <v>3</v>
@@ -10101,7 +10101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10600,22 +10600,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•上海世纪公园</t>
+          <t>华为授权体验店（蜀新天街）</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>成都市</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>上海市浦东新区罗山路1589号</t>
+          <t>四川省成都市郫都区望丛中路1199号成都蜀新天街 A 馆1F-29号30号</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -10632,27 +10632,27 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京来广营西路</t>
+          <t>华为智能生活馆•合肥高新银泰城</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>合肥市</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区来广营西路甲9号</t>
+          <t>安徽省合肥市高新区望江西路888号银泰百 F11023-1024号华为授权服务中心</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10664,27 +10664,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•北京王四营</t>
+          <t>华为智能生活馆•马鞍山金鹰国际广场</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>马鞍山市</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>北京市朝阳区王四营339号</t>
+          <t>安徽省马鞍山市花山区湖西南路8号金鹰国际购物中心A01层F1018B商铺</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10696,27 +10696,27 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•通化新胜北路</t>
+          <t>华为授权体验店（济南新辰天地）</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>通化市</t>
+          <t>济南市</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>吉林省通化市新胜北路2459号</t>
+          <t>山东省济南市历城区唐冶中路5199号银座·新辰天地L1层005号铺</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10728,27 +10728,27 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>华为授权体验店（蜀新天街）</t>
+          <t>华为授权体验店（万象汇）</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>成都市</t>
+          <t>济宁市</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>四川省成都市郫都区望丛中路1199号成都蜀新天街 A 馆1F-29号30号</t>
+          <t>山东省济宁市高新区海川路77号万象汇L152号商铺</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
         </is>
       </c>
     </row>
@@ -10760,22 +10760,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•合肥高新银泰城</t>
+          <t>鸿蒙智行智界用户中心•东莞常平环常南路</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>合肥市</t>
+          <t>东莞市</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>安徽省合肥市高新区望江西路888号银泰百 F11023-1024号华为授权服务中心</t>
+          <t>广东省东莞市常平环常南路10号102室</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -10792,22 +10792,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•马鞍山金鹰国际广场</t>
+          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>马鞍山市</t>
+          <t>佛山市</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>安徽省马鞍山市花山区湖西南路8号金鹰国际购物中心A01层F1018B商铺</t>
+          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>华为授权体验店（济南新辰天地）</t>
+          <t>鸿蒙智行智界用户中心•汕头东海岸新城</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>济南市</t>
+          <t>汕头市</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>山东省济南市历城区唐冶中路5199号银座·新辰天地L1层005号铺</t>
+          <t>广东省汕头市龙湖区武夷山路1号瑞讯海湾汽车生活广场1号楼智界门店</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10856,27 +10856,27 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>华为授权体验店（万象汇）</t>
+          <t>华为智能生活馆•柳州风晴港</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>济宁市</t>
+          <t>柳州市</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>山东省济宁市高新区海川路77号万象汇L152号商铺</t>
+          <t>广西壮族自治区柳州市城中区中山中路9号柳州风情港2栋1-1号</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
+          <t>全新</t>
         </is>
       </c>
     </row>
@@ -10888,22 +10888,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•东莞常平环常南路</t>
+          <t>华为授权体验店（南大街）</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东莞市</t>
+          <t>南通市</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>广东省东莞市常平环常南路10号102室</t>
+          <t>江苏省南通市崇川区环城南路88号华为授权体验店</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10920,22 +10920,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙执行授权用户中心•佛山禅城大道</t>
+          <t>华为智能生活馆•南昌新城吾悦</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>佛山市</t>
+          <t>南昌市</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>广东省佛山市禅城区石湾镇街道塘头商贸城二号楼前排1号正东方向180米</t>
+          <t>江西省南昌市青山湖区艾溪湖北路77号新城吾悦广场一层10003-1</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10952,22 +10952,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•汕头东海岸新城</t>
+          <t>华为授权体验店（未来广场）</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>汕头市</t>
+          <t>赣州市</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>广东省汕头市龙湖区武夷山路1号瑞讯海湾汽车生活广场1号楼智界门店</t>
+          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -10984,22 +10984,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>华为智能生活馆•柳州风晴港</t>
+          <t>华为授权体验店（青悦城）</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>柳州市</t>
+          <t>台州市</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>广西壮族自治区柳州市城中区中山中路9号柳州风情港2栋1-1号</t>
+          <t>浙江省台州市椒江区中心大道555号青悦城111-2-112号商铺华为授权体验店</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -11016,22 +11016,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>华为授权体验店（南大街）</t>
+          <t>华为授权体验店（福州仓山世纪金源）</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>南通市</t>
+          <t>福州市</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区环城南路88号华为授权体验店</t>
+          <t>福州市仓山区潘墩路188号世纪金源购物中心3号门华为体验店</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -11048,22 +11048,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•宜兴融达汽车城</t>
+          <t>华为智能生活馆•咸阳丽彩万达</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>咸阳市</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>江苏省无锡市宜兴市西氿大道92号</t>
+          <t>陕西省咸阳市秦都区玉泉东路10号咸阳丽彩万达广场1028号商铺（1F-C，2F-C）</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -11080,281 +11080,25 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•镇江官塘桥路</t>
+          <t>鸿蒙智行智界用户中心•安康钻石中路</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>镇江市</t>
+          <t>安康市</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>江苏省镇江市润州区官塘桥路299号</t>
+          <t>陕西省安康市高新区钻石中路2号（鸿蒙智行）</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•南昌新城吾悦</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>南昌市</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>江西省南昌市青山湖区艾溪湖北路77号新城吾悦广场一层10003-1</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>华为授权体验店（未来广场）</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>赣州市</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>江西省赣州市南康区远洋未来广场1层F1040+F1041+F1042+F1043B+F1026+W1008</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•衡水昌明街</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>衡水市</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>河北省衡水市昌明大街与胜利西路交叉口西南角</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>华为授权体验店（青悦城）</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>台州市</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>浙江省台州市椒江区中心大道555号青悦城111-2-112号商铺华为授权体验店</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•三亚迎宾大道</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>海南</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>三亚市</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>海南省三亚市吉阳区迎宾路393号</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>回归（曾出现 20260504~20260504，疑似此前漏爬）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>华为授权体验店（福州仓山世纪金源）</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>福州市</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>福州市仓山区潘墩路188号世纪金源购物中心3号门华为体验店</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•咸阳丽彩万达</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>咸阳市</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>陕西省咸阳市秦都区玉泉东路10号咸阳丽彩万达广场1028号商铺（1F-C，2F-C）</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>全新</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>鸿蒙智行智界用户中心•安康钻石中路</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>安康市</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>陕西省安康市高新区钻石中路2号（鸿蒙智行）</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>全新</t>
         </is>
@@ -11371,7 +11115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -11710,7 +11454,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11725,7 +11469,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11742,7 +11486,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11757,7 +11501,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -11902,7 +11646,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -11917,7 +11661,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11934,7 +11678,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11949,7 +11693,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -11998,7 +11742,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -12013,7 +11757,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -12030,7 +11774,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -12045,7 +11789,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -12190,7 +11934,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -12205,7 +11949,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -12222,7 +11966,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -12237,7 +11981,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12819,102 +12563,6 @@
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>连续在档 2 期</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•郑州中福汽车城</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>郑州市</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>河南省郑州市经北六路与中州大道交叉口东800米路南中福汽车城7号</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 2 期；本期同名店仍在档（地址写法变更，非关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•宜昌发展大道</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>宜昌市</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>湖北省宜昌市西陵区发展大道44号</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 2 期；本期同名店仍在档（地址写法变更，非关店）</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•衡阳杨柳汽车城</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>衡阳市</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>湖南省衡阳市蒸湘区杨柳汽贸城一期101号</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>连续在档 2 期；本期同名店仍在档（地址写法变更，非关店）</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12980,17 +12628,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -13000,7 +12648,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -13012,17 +12660,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -13032,7 +12680,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -13071,22 +12719,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•苏州凯马汽车城</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -13096,29 +12744,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市吴中区中山东路156号 → 江苏省苏州市吴中区木渎镇中山东路156号5幢</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•张家港攀华汽车城</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13128,7 +12776,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省苏州市张家港市杨舍镇经济开发区东千泾路68号（临时营业） → 江苏省苏州市张家港市经济开发区东区大道北首1号</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -13167,22 +12815,22 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -13192,29 +12840,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -13224,29 +12872,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•阳泉开发区大连街</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -13256,29 +12904,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>山西省阳泉市高新区五渡园区大连街517号 → 山西省阳泉高新技术产业开发区大连街517号101室</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -13288,29 +12936,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -13320,7 +12968,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -13332,17 +12980,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13352,29 +13000,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•朔州振华汽车城</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13384,7 +13032,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>山西省朔州市开发区振华东街振华车城A3号 → 山西省朔州市经济开发区振华东街振华车城A3号-1</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -13423,22 +13071,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13448,29 +13096,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13480,14 +13128,14 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -13497,44 +13145,44 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车保山联通汽车城销售展厅</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13544,29 +13192,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13576,29 +13224,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13608,29 +13256,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行智界用户中心•南宁五象钜荣汽车园</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13640,29 +13288,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市良庆区平乐大道49号钜荣汽车园内 → 中国（广西）自由贸易试验区南宁片区平乐大道49号钜荣汽车园内</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南京江北新区</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13672,39 +13320,39 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>江苏省南京市浦口区浦珠南路8号 → 江苏省南京市江北新区浦珠南路8号</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售中心</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>店名变更</t>
+          <t>地址变更</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车保山联通汽车城销售展厅 → 小鹏汽车保山联通汽车城销售中心</t>
+          <t>地址归一前缀一致</t>
         </is>
       </c>
     </row>
@@ -13716,17 +13364,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13743,22 +13391,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13775,352 +13423,128 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>地址归一前缀一致</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>地址归一前缀一致</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>MAEXTRO尊界体验中心•北京三里屯</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尊界用户中心•北京三里屯</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>地址归一前缀一致</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>地址变更</t>
+          <t>店名变更</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>保时捷</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>海宁保时捷中心</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>地址变更</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>地址归一前缀一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>店名相似度 97%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>浙江</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
           <t>店名相似度 86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>小米</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>店名相似度 79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>小鹏</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>店名变更</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>15</v>
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8566</v>
+        <v>8565</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8552</v>
+        <v>8551</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>-14</v>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="C422" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D422" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E422" s="3" t="n">
         <v>0</v>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,14 +12680,14 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -12697,12 +12697,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -12761,12 +12761,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13401,12 +13401,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13480,29 +13480,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（30家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（44家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（29条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（30家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（44家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（29条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,14 +12744,14 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -12761,12 +12761,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -12825,12 +12825,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13199,22 +13199,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13295,22 +13295,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13401,12 +13401,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13428,17 +13428,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13480,29 +13480,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,29 +13512,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -12655,7 +12655,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -12751,22 +12751,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -12825,12 +12825,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -12921,12 +12921,12 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -13177,12 +13177,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13295,22 +13295,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13401,12 +13401,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13497,12 +13497,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,29 +13512,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（30家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（44家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（29条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（30家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（44家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（29条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -12655,22 +12655,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -12820,17 +12820,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13199,22 +13199,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13295,22 +13295,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13401,12 +13401,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
@@ -13487,22 +13487,22 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（30家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（44家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（29条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="新增网点（30家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="减少网点（44家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="变更明细（29条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12783,22 +12783,22 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,29 +12872,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13199,22 +13199,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13295,22 +13295,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
+          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
+          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>小米汽车河南郑州巩义正上豪布斯卡</t>
+          <t>小米汽车河南郑州新郑龙湖锦艺城</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>河南省巩义市滨河路与石河路交叉口豪布斯卡广场一楼小米汽车展台</t>
+          <t>郑新快速路与双湖大道交界处东北角龙湖锦艺城一楼小米汽车展台</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -12623,22 +12623,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,29 +12840,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13480,29 +13480,29 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11934,7 +11934,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
+          <t>小米汽车福建漳州龙文区碧湖万达</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
+          <t>万达店(漳州碧湖万达广场店)</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>小米汽车福建漳州龙文区碧湖万达</t>
+          <t>小米汽车福建漳州龙文区龙文吾悦广场</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>万达店(漳州碧湖万达广场店)</t>
+          <t>福建省漳州市龙文区步港路8号—漳州吾悦广场中庭</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -12623,22 +12623,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,29 +12680,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,14 +12776,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,29 +13032,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,29 +13064,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13295,22 +13295,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13359,22 +13359,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13401,12 +13401,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13423,22 +13423,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
@@ -13492,17 +13492,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,29 +13512,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12884,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
@@ -13071,22 +13071,22 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -13177,12 +13177,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13199,22 +13199,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店(东江之星)</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>华为授权体验店（东江之星）</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13231,22 +13231,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>华为授权体验店(东江之星)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>华为授权体验店（东江之星）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13295,22 +13295,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13433,12 +13433,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳银泰广场</t>
+          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江金华东阳宝龙广场</t>
+          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13448,29 +13448,29 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 86%</t>
+          <t>店名相似度 97%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江绍兴市新昌县绍兴新昌万达</t>
+          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 97%</t>
+          <t>店名相似度 92%</t>
         </is>
       </c>
     </row>
@@ -13492,17 +13492,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
+          <t>小米汽车浙江金华东阳银泰广场</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
+          <t>小米汽车浙江金华东阳宝龙广场</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -13512,29 +13512,29 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 79%</t>
+          <t>店名相似度 86%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰汽车城销售服务中心</t>
+          <t>小米汽车安徽蚌埠蚌山区蚌埠银泰百货</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青峰国际汽车城销售服务中心</t>
+          <t>小米之家安徽省蚌埠市蚌山区蚌埠银泰百货汽车体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 92%</t>
+          <t>店名相似度 79%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260511_vs_20260518.xlsx
@@ -11454,7 +11454,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京海淀区城乡购物中心</t>
+          <t>小米汽车北京丰台区丽泽龙湖天街</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>城乡购物中心一层中庭</t>
+          <t>丽泽龙湖一层中庭</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>小米汽车北京丰台区丽泽龙湖天街</t>
+          <t>小米汽车北京海淀区城乡购物中心</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>丽泽龙湖一层中庭</t>
+          <t>城乡购物中心一层中庭</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
+          <t>小米汽车江苏无锡宜兴宝龙</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>梁溪路35号滨湖万达广场一楼中庭</t>
+          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>小米汽车江苏无锡宜兴宝龙</t>
+          <t>小米汽车江苏无锡滨湖区无锡滨湖万达</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>东坡西路与白宕北路交汇处宜兴宝龙广场一楼中庭</t>
+          <t>梁溪路35号滨湖万达广场一楼中庭</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德大良卫星店</t>
+          <t>佛山顺德世维4S中心</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
+          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>佛山顺德世维4S中心</t>
+          <t>佛山顺德大良卫星店</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>佛山市顺德区北滘105国道碧江路段佛陈路口</t>
+          <t>广东省佛山市顺德区大良街道新松社区广珠公路顺德路段新松口仓库铺位之三号（住所申报）</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -12628,17 +12628,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
+          <t>小鹏汽车安庆英德利销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12648,29 +12648,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
+          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>宾利昆明</t>
+          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
+          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
         </is>
       </c>
     </row>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛重庆路销售服务中心</t>
+          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
+          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
+          <t>小鹏汽车廊坊霸州销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
+          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车安庆英德利销售服务中心</t>
+          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>安庆市英德利国际汽车城松祥路与福旺路交叉口北60米 → 安徽省安庆市英德利国际汽车城福旺路</t>
+          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸宁南汽车园销售服务中心</t>
+          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>咸宁市咸安区咸安经济开发区通江大道32号 → 咸宁市咸安区通江大道19号</t>
+          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小米汽车福建宁德蕉城区宁德万达</t>
+          <t>小鹏汽车青岛重庆路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
+          <t>青岛市市北区长沙路49-6号 → 山东省青岛市市北区重庆南路218-2号</t>
         </is>
       </c>
     </row>
@@ -12852,17 +12852,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车廊坊霸州销售服务中心</t>
+          <t>小鹏汽车河源大道销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12872,14 +12872,14 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省廊坊市霸州市106国道王伍房南路东 → 河北省廊坊市霸州市106国道王伍房南道南50米路东</t>
+          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -12889,12 +12889,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>宾利北京 - 三里屯</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
+          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米汽车四川泸州纳溪区蓝安路授权服务中心</t>
+          <t>小鹏汽车遵义新龙大道销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12936,14 +12936,14 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>泸州市龙达汽车销售服务有限公司 → 四川省泸州市纳溪区东升街道蓝安路三段19号2号楼5层102号</t>
+          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>宾利</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -12953,12 +12953,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>宾利北京 - 三里屯</t>
+          <t>小鹏汽车北京清河安宁庄销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12968,29 +12968,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>龙跃街9号院 顺义区马坡聚源工业园 101300 → 龙跃街9号院 顺义区马坡聚源工业园 101317</t>
+          <t>北京市海淀区安宁庄后街南1号C区1层1301号 → 北京市海淀区清河街道西三旗桥向南600米路西小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>宾利</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
+          <t>宾利昆明</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
+          <t>第四大道S107-S109 前兴路润城 650103 → 第四大道S107-S109 前兴路润城 650228</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车遵义新龙大道销售服务中心</t>
+          <t>小米汽车浙江省嘉兴市经济技术开发区城南汽车城零售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺接到和平村汽车博览中心小鹏汽车销售中心1-1号 → 贵州省遵义市红花岗区奥体路与新龙大道交叉口东北方向131米左右</t>
+          <t>嘉兴经济开发区320国道南园大道交叉口 → 嘉杭路1179号小米汽车</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家江西省赣州市章贡区赣州万象城汽车体验店</t>
+          <t>小米汽车福建宁德蕉城区宁德万达</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江西赣州市章贡区水南镇水南镇登峰大道8号万象城135号铺位 → 江西省赣州市章贡区登峰大道华润万象城一楼L135铺小米之家汽车体验店</t>
+          <t>天湖东路 1 号 1 号门 → 宁化街道苏宁广场A区1号门旁</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车河源大道销售服务中心</t>
+          <t>小鹏汽车驻马店金龙汽车园销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河源市源城区河源大道南中裕丰田汽车旁 → 广东省河源市源城区河源大道南中国石油南侧250米</t>
+          <t>开源大道与兴业大道交叉口金龙科技园西门北侧1-4跨 → 开源大道东金龙科技园区16号厂房自西到东1-8跨，自北到南1-4跨</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车青岛青锋国际汽车城销售服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>青岛市市北区四流南路22号-8幢展厅 → 山东省青岛市市北区水清沟大沙支路2号</t>
+          <t>北京经济技术开发区双羊路15号 → 北京市经济技术开发区科创三街15号A1幢</t>
         </is>
       </c>
     </row>
@@ -13167,22 +13167,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
+          <t>小米汽车山东济宁任城区济宁太白路万达</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
+          <t>小米汽车山东省济宁市任城区济宁运河城</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现4S中心</t>
+          <t>衡水蓝池赛龙4S中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>湘潭九现卫星店</t>
+          <t>衡水蓝池赛龙卫星店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13263,22 +13263,22 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷中心</t>
+          <t>鸿蒙智行授权用户中心•深圳体育中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>海宁保时捷认可易手车及售后服务中心</t>
+          <t>鸿蒙智行授权用户中心•福田深圳体育中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13300,17 +13300,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙4S中心</t>
+          <t>营口中升沃盛4S中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>衡水蓝池赛龙卫星店</t>
+          <t>营口中升沃盛卫星店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13327,22 +13327,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
+          <t>海宁保时捷中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
+          <t>海宁保时捷认可易手车及售后服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛4S中心</t>
+          <t>湘潭九现4S中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>营口中升沃盛卫星店</t>
+          <t>湘潭九现卫星店</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13391,22 +13391,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东济宁任城区济宁太白路万达</t>
+          <t>鸿蒙智行授权用户中心•深圳龙观大道</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小米汽车山东省济宁市任城区济宁运河城</t>
+          <t>鸿蒙智行授权用户中心•深圳龙华龙观大道</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
